--- a/AAII_Financials/Quarterly/TATYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TATYY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="92">
   <si>
     <t>TATYY</t>
   </si>
@@ -656,22 +656,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -686,103 +685,111 @@
     <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43373</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43190</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43008</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42825</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42643</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42460</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42277</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42094</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -819,53 +826,59 @@
       <c r="N8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="3">
         <v>860800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>812300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>754900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1781800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1831400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1622900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1687100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1789300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1978300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1891400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1626900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>1545600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1526000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>1502500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>1580100</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -947,8 +960,14 @@
       <c r="AC9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1030,8 +1049,14 @@
       <c r="AC10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1061,8 +1086,10 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1144,8 +1171,14 @@
       <c r="AC12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1227,8 +1260,14 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1265,21 +1304,21 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
         <v>77400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>24900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>19100</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1289,20 +1328,20 @@
       <c r="V14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>5</v>
@@ -1310,8 +1349,14 @@
       <c r="AC14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1348,21 +1393,21 @@
       <c r="N15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="3">
         <v>6600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>27600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>6400</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1372,20 +1417,20 @@
       <c r="V15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
-      </c>
-      <c r="X15" s="3">
-        <v>0</v>
+      <c r="W15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA15" s="3" t="s">
-        <v>5</v>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>5</v>
@@ -1393,8 +1438,14 @@
       <c r="AC15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1421,8 +1472,10 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1459,53 +1512,59 @@
       <c r="N17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="3">
         <v>817500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>753200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>664300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1617100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1625400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1477400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1549300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1618800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1744800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1747400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1474200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1472600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1433400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1548500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1490600</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1542,53 +1601,59 @@
       <c r="N18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="3">
         <v>43300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>59000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>90500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>164700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>206000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>145500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>137800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>170500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>233500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>144000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>152700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>73000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>92600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-46100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>89500</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1618,8 +1683,10 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1656,53 +1723,59 @@
       <c r="N20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-15700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-17100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-16600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>2500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-2500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>4700</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-5700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>4900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>17000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>11700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>10500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1739,53 +1812,59 @@
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
         <v>107600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>156200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>186200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>262300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>323800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>241300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>229300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>276800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>335400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>244300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>242600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>168300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>176100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>40800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>167200</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1822,11 +1901,11 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1837,11 +1916,11 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>5</v>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>5</v>
@@ -1855,20 +1934,26 @@
       <c r="Y22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB22" s="3">
         <v>17000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>13000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>14500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1905,53 +1990,59 @@
       <c r="N23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="3">
         <v>27600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>42000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>74000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>167300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>203500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>150200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>137800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>170500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>227800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>138700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>157600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>73000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>91300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-50000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>83000</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1988,53 +2079,59 @@
       <c r="N24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q24" s="3">
         <v>17100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>20400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>22800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>40900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>31900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>39000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-19100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>52400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-27700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>2600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>3900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>13200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2116,8 +2213,14 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2154,53 +2257,59 @@
       <c r="N26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="3">
         <v>10500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>45900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>53600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>144500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>162500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>118300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>98800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>189600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>175500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>166400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>158900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>70400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>87400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-63200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>68500</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2237,53 +2346,59 @@
       <c r="N27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="3">
         <v>10500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>45900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>53600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>144500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>162500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>118300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>98800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>189600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>175500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>166400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>158900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>70400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>87400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-63200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>68500</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2365,8 +2480,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2403,53 +2524,59 @@
       <c r="N29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="3">
         <v>123300</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>111500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>116000</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>2700</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>1200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>78300</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>-23500</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
         <v>13200</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AE29" s="3">
         <v>21100</v>
       </c>
     </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2531,8 +2658,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2614,8 +2747,14 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2652,53 +2791,59 @@
       <c r="N32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3">
         <v>15700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>17100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>16600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-2500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>2500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-4700</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>5700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>5300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-17000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-11700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2735,53 +2880,59 @@
       <c r="N33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="3">
         <v>133800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>157500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>169600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>144500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>162500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>118300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>98800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>192300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>175500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>166400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>160100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>148700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>63900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-50000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>89500</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2863,8 +3014,14 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2901,141 +3058,153 @@
       <c r="N35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="3">
         <v>133800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>157500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>169600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>144500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>162500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>118300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>98800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>192300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>175500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>166400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>160100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>148700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>63900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-50000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>89500</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43373</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43190</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43008</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42825</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42643</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42460</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42277</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42094</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3065,8 +3234,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3096,91 +3267,99 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>454200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>463000</v>
+      </c>
+      <c r="F41" s="3">
         <v>436900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>445300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>431500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>418100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>796100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>750700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>551900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>556600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>477100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>496900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>587600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>505200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>486800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>617100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>343400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>447900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>337100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>346500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>259100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>342500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>344700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>355900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>413500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>305200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>256800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>425300</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3221,215 +3400,233 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>42000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>48500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>84900</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y42" s="3">
         <v>1400</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
         <v>4900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>5200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>7800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>23700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>521500</v>
+        <v>521600</v>
       </c>
       <c r="E43" s="3">
         <v>531600</v>
       </c>
       <c r="F43" s="3">
-        <v>484500</v>
+        <v>521500</v>
       </c>
       <c r="G43" s="3">
-        <v>469500</v>
+        <v>531600</v>
       </c>
       <c r="H43" s="3">
+        <v>483200</v>
+      </c>
+      <c r="I43" s="3">
+        <v>468200</v>
+      </c>
+      <c r="J43" s="3">
         <v>372600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>351300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>354900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>357900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>369800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>385100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>425600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>343800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>433000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>406800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>422000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>397100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>389200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>425700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>402300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>450000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>385700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>374400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>396500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>363900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>384500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>495100</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>755300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>769900</v>
+      </c>
+      <c r="F44" s="3">
         <v>735300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>749400</v>
       </c>
-      <c r="F44" s="3">
-        <v>750700</v>
-      </c>
-      <c r="G44" s="3">
-        <v>727400</v>
-      </c>
       <c r="H44" s="3">
+        <v>723500</v>
+      </c>
+      <c r="I44" s="3">
+        <v>701100</v>
+      </c>
+      <c r="J44" s="3">
         <v>434300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>409500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>445800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>449600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>499100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>519800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>551800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>345100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>698100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>498600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>577900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>512500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>513400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>508700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>571400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>537700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>582500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>449500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>507400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>443500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>478000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>331800</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3437,414 +3634,444 @@
         <v>1300</v>
       </c>
       <c r="E45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G45" s="3">
         <v>1400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>5200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>5000</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3">
         <v>1200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>3700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1804300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>48600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>11500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>6300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>44700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>56800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>46400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>32700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>55200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>40900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>71400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>65200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>348300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>81600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>143500</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1761500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1795400</v>
+      </c>
+      <c r="F46" s="3">
         <v>1695000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1727600</v>
       </c>
-      <c r="F46" s="3">
-        <v>1701600</v>
-      </c>
-      <c r="G46" s="3">
-        <v>1648800</v>
-      </c>
       <c r="H46" s="3">
+        <v>1673100</v>
+      </c>
+      <c r="I46" s="3">
+        <v>1621200</v>
+      </c>
+      <c r="J46" s="3">
         <v>1603000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1511500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1372900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1384600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1347200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1403000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1588500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2998400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1708500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1582400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1434600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1402100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1296500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1327300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1265600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1386800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1353800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1256200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1387800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1468700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1224600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1398400</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>41700</v>
+      </c>
+      <c r="F47" s="3">
         <v>40300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>41100</v>
-      </c>
-      <c r="F47" s="3">
-        <v>36200</v>
-      </c>
-      <c r="G47" s="3">
-        <v>35100</v>
       </c>
       <c r="H47" s="3">
         <v>36200</v>
       </c>
       <c r="I47" s="3">
+        <v>35100</v>
+      </c>
+      <c r="J47" s="3">
+        <v>36200</v>
+      </c>
+      <c r="K47" s="3">
         <v>34100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>243800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>245800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>290400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>302400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>298100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>66900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>215200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>209100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>195200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>198500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>192800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>158600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>170500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>154200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>167700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>136700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>137000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>180000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>453000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>476700</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1846000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1881600</v>
+      </c>
+      <c r="F48" s="3">
         <v>1842900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1878300</v>
       </c>
-      <c r="F48" s="3">
-        <v>1839800</v>
-      </c>
-      <c r="G48" s="3">
-        <v>1782700</v>
-      </c>
       <c r="H48" s="3">
+        <v>1823000</v>
+      </c>
+      <c r="I48" s="3">
+        <v>1766500</v>
+      </c>
+      <c r="J48" s="3">
         <v>705000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>664800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>666900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>672500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>616300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>641800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>603700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>559000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1450000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2937800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1508100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1475300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1161600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1206500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>1316100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>1416500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>1401400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>1272200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>1207800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1006900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>987600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>995500</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1028600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1048500</v>
+      </c>
+      <c r="F49" s="3">
         <v>1071300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1091900</v>
       </c>
-      <c r="F49" s="3">
-        <v>1028400</v>
-      </c>
-      <c r="G49" s="3">
-        <v>996500</v>
-      </c>
       <c r="H49" s="3">
+        <v>1062000</v>
+      </c>
+      <c r="I49" s="3">
+        <v>1029100</v>
+      </c>
+      <c r="J49" s="3">
         <v>504000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>475200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>488800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>492900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>524700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>546400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>533200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>380500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>452700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>406800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>430900</v>
-      </c>
-      <c r="S49" s="3">
-        <v>431800</v>
-      </c>
-      <c r="T49" s="3">
-        <v>404600</v>
       </c>
       <c r="U49" s="3">
         <v>431800</v>
       </c>
       <c r="V49" s="3">
+        <v>404600</v>
+      </c>
+      <c r="W49" s="3">
+        <v>431800</v>
+      </c>
+      <c r="X49" s="3">
         <v>491000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>539200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>529600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>511100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>508700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>403000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>447700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>418700</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3926,8 +4153,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4009,91 +4242,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>129400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>131900</v>
+      </c>
+      <c r="F52" s="3">
         <v>133100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>135600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>143400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>139000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>53600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>50600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>50500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>51000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>45200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>47000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>35900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>86600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>66900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>53600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>44400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>42200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>248400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>241500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>263200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>206600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>207400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>67700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>90000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>114800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>77700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>39500</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4175,91 +4420,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4840900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>4934100</v>
+      </c>
+      <c r="F54" s="3">
         <v>4837800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>4930800</v>
       </c>
-      <c r="F54" s="3">
-        <v>4820500</v>
-      </c>
-      <c r="G54" s="3">
-        <v>4670900</v>
-      </c>
       <c r="H54" s="3">
+        <v>4808800</v>
+      </c>
+      <c r="I54" s="3">
+        <v>4659700</v>
+      </c>
+      <c r="J54" s="3">
         <v>2963400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2794200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2882100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2906700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2843300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2960900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>3101500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>4091400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>3893300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>3720700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>3613100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>3549900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>3303800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>3365700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>3506300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>3703300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>3659900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>3244000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>3331200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>3173400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>3190600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>3328800</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4289,8 +4546,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4320,506 +4579,544 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>355200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>362000</v>
+      </c>
+      <c r="F57" s="3">
         <v>469100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>478100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>301000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>291700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>345800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>326100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>219800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>221600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>329500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>343100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>309300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>276900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>350400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>424600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>468900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>378400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>404600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>431800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>425500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>447200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>416000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>397800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>439600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>439600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>416100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>425300</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>26900</v>
+      </c>
+      <c r="F58" s="3">
         <v>208400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>212400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>208000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>201600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>22800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>21500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>21500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>21700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>52500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>54600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>149700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>32800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>74800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>107100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>50700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>317600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>265000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>29300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>21800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>39600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>116200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>129300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>260900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>644300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>401600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>468800</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>166400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>169600</v>
+      </c>
+      <c r="F59" s="3">
         <v>95400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>97300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>140800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>136500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>105900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>99800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>101000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>101900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>85400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>89000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>117500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>679700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>325400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>104600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>124200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>143900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>136000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>135400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>100900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>113200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>110900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>150300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>147400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>159100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>109300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>142200</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>651000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>663500</v>
+      </c>
+      <c r="F60" s="3">
         <v>772900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>787800</v>
       </c>
-      <c r="F60" s="3">
-        <v>786800</v>
-      </c>
-      <c r="G60" s="3">
-        <v>762400</v>
-      </c>
       <c r="H60" s="3">
+        <v>789400</v>
+      </c>
+      <c r="I60" s="3">
+        <v>764900</v>
+      </c>
+      <c r="J60" s="3">
         <v>474500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>447400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>426900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>430500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>467400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>486700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>707600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>989400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>730900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>582700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>643800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>840000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>805600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>596500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>548200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>600000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>643200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>677400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>847800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>1243000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>927000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>1036300</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1682300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1714700</v>
+      </c>
+      <c r="F61" s="3">
         <v>1523000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1552300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1479300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1433500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>721100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>679900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>723700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>729900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>728500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>758700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>732400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>917200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>978900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1020100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>864300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>667600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>441200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>703900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>755500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>812300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>797800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>731600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>725200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>371700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>609700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>579400</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>50200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>51100</v>
+      </c>
+      <c r="F62" s="3">
         <v>67200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>68500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>77500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>75100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>4000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>3800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>2500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>2500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>4900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>5100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>6200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>206000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>275600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>303500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>332000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>332500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>295700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>342800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>338200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>459900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>459600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>456900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>416100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>400400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>421400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>337100</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4901,8 +5198,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4984,8 +5287,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5067,91 +5376,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2730700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2783300</v>
+      </c>
+      <c r="F66" s="3">
         <v>2759600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2812700</v>
       </c>
-      <c r="F66" s="3">
-        <v>2768800</v>
-      </c>
-      <c r="G66" s="3">
-        <v>2682900</v>
-      </c>
       <c r="H66" s="3">
+        <v>2757100</v>
+      </c>
+      <c r="I66" s="3">
+        <v>2671600</v>
+      </c>
+      <c r="J66" s="3">
         <v>1361700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1284000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1317300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1328500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1366800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1423300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1629300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2114000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1986700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1906300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1840100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1840100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1542500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1643200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1642000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1872200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1900600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1865900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1990400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>2016500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1959400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1954100</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5181,8 +5502,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5264,8 +5587,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5347,8 +5676,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5430,8 +5765,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5513,91 +5854,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>652300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>664900</v>
+      </c>
+      <c r="F72" s="3">
         <v>641200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>653500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>611100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>592200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>851100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>802500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>786800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>793500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>678500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>706600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>634600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>1289900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1219000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1146300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>1110200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>1060900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>1142700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1084500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>1151000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>1091000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>1068500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>734000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>658700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>474800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>542500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>686000</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5679,8 +6032,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5762,8 +6121,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5845,91 +6210,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2110100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2150700</v>
+      </c>
+      <c r="F76" s="3">
         <v>2078100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2118100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2054300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1990600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1600300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1509000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1563600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1576900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1475400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1536400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1471000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1977500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1906600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1814500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1773000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1709800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1761300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1722500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1864300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1831200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1759300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>1378200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>1340800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>1156900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1231200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>1374700</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6011,96 +6388,108 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43373</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43190</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43008</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42825</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42643</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42460</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42277</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42094</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6137,53 +6526,59 @@
       <c r="N81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q81" s="3">
         <v>133800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>157500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>169600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>144500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>162500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>118300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>98800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>192300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>175500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>166400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>160100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>148700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>63900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-50000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>89500</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6213,91 +6608,99 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>36300</v>
+      </c>
+      <c r="F83" s="3">
         <v>18800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>17700</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3">
         <v>17700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>18400</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>16200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>17600</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3">
         <v>80000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>114200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>112200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>95000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>120400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>91100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>91500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>106400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>107500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>105700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>85000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>78300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>71700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>76400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6379,8 +6782,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6462,8 +6871,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6545,8 +6960,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6628,8 +7049,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6711,91 +7138,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>75300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>76700</v>
+      </c>
+      <c r="F89" s="3">
         <v>78000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>79500</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H89" s="3">
+        <v>38100</v>
+      </c>
+      <c r="I89" s="3">
+        <v>36900</v>
+      </c>
+      <c r="J89" s="3">
         <v>70400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>66300</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
         <v>52500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>54600</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="3">
         <v>234900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>162700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>312400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>196400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>285400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>140800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>257400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>105000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>295800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>130800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>245100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>19600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>225600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>72400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>163300</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6825,91 +7264,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-43600</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-44400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-33600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-34300</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H91" s="3">
+        <v>-43300</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-41900</v>
+      </c>
+      <c r="J91" s="3">
         <v>-31500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-29700</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N91" s="3">
         <v>-25600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-26700</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-67000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-83000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-69000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-94000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-73000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-67400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-56100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-81800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-72200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-76600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-85000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-133000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-100400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-216000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-192300</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6991,8 +7438,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7074,91 +7527,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-42300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-43100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-32900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-33600</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H94" s="3">
+        <v>-561400</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-544000</v>
+      </c>
+      <c r="J94" s="3">
         <v>160200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>151000</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
         <v>-7300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-7600</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-53800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-190300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-76500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-106500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-55800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-95800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-36600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-83200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-58000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-87200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-59100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>183900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-71700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-108000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-108000</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7188,91 +7653,99 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E96" s="3">
+        <v>19500</v>
+      </c>
+      <c r="F96" s="3">
         <v>39700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>40400</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H96" s="3">
+        <v>18700</v>
+      </c>
+      <c r="I96" s="3">
+        <v>18200</v>
+      </c>
+      <c r="J96" s="3">
         <v>34200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>32200</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N96" s="3">
         <v>31700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>33000</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-133800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-52500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-123700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-50700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-120400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-47300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-114700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-53200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-130200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-50200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-113300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-49600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-120000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-50000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-121100</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7354,8 +7827,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7437,8 +7916,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7520,253 +8005,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-46400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-47300</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H100" s="3">
+        <v>336600</v>
+      </c>
+      <c r="I100" s="3">
+        <v>326100</v>
+      </c>
+      <c r="J100" s="3">
         <v>-103200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-97300</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
         <v>-97000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-101000</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-158800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-82700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>43400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-188800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-153900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-46100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-123200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-80500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-244800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-93800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-247600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-116100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-100400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-151400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-92200</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E101" s="3">
+        <v>18200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-22100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-20900</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
         <v>51300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>55900</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
         <v>10500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-38100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-7700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-15200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>18600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>2400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>17100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-12300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-19800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>13200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>27100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>20900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>18400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>12800</v>
+      </c>
+      <c r="F102" s="3">
         <v>-6000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-6200</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>-168000</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-162800</v>
+      </c>
+      <c r="J102" s="3">
         <v>105200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>99200</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-51300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-53400</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>32800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-148300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>271600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-114100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>94300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>1200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>114700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-70900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-26900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-37000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-34500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>108300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>50900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-168500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-30300</v>
       </c>
     </row>
